--- a/04_Figures/F04_association/modules/acute/limma/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/acute/limma/c_data/results.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -492,16 +486,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000244935960219656</v>
+        <v>-0.00790987953422933</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.042309240551379</v>
+        <v>-1.46315455352442</v>
       </c>
       <c r="F2" t="n">
-        <v>0.96630212404577</v>
+        <v>0.145619624406515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.96630212404577</v>
+        <v>0.274513196975048</v>
       </c>
     </row>
     <row r="3">
@@ -515,16 +509,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0136533776194655</v>
+        <v>0.0000864805967239841</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.35842886247792</v>
+        <v>0.0159970171910507</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0194957601192651</v>
+        <v>0.987259068789736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.136403179065933</v>
+        <v>0.987259068789736</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +532,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00982539706787667</v>
+        <v>-0.0148908272875113</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6971990869973</v>
+        <v>-2.75447706342226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0914998438346456</v>
+        <v>0.00664307780169112</v>
       </c>
       <c r="G4" t="n">
-        <v>0.237899593970079</v>
+        <v>0.0730738558186023</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00106999974965838</v>
+        <v>0.00988655660777212</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.184827400425864</v>
+        <v>1.82879653940875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.853586030283734</v>
+        <v>0.069513599053794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.954943359470877</v>
+        <v>0.254883196530578</v>
       </c>
     </row>
     <row r="6">
@@ -584,16 +578,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00423178166910175</v>
+        <v>-0.00464951811567305</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.730980736509158</v>
+        <v>-0.860059065779961</v>
       </c>
       <c r="F6" t="n">
-        <v>0.465803162705577</v>
+        <v>0.391196089389778</v>
       </c>
       <c r="G6" t="n">
-        <v>0.756930139396563</v>
+        <v>0.478128553698617</v>
       </c>
     </row>
     <row r="7">
@@ -607,16 +601,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00242046551267901</v>
+        <v>-0.0000888947431936603</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.418101358128118</v>
+        <v>-0.0164435814382931</v>
       </c>
       <c r="F7" t="n">
-        <v>0.676403785912409</v>
+        <v>0.986903431552996</v>
       </c>
       <c r="G7" t="n">
-        <v>0.937244045871245</v>
+        <v>0.987259068789736</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +624,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00086438942728428</v>
+        <v>0.0106944751743389</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.149311110447981</v>
+        <v>1.97824378755377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.881486177973118</v>
+        <v>0.0498228366595706</v>
       </c>
       <c r="G8" t="n">
-        <v>0.954943359470877</v>
+        <v>0.254883196530578</v>
       </c>
     </row>
     <row r="9">
@@ -653,16 +647,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.011015429705269</v>
+        <v>-0.00605770533341991</v>
       </c>
       <c r="E9" t="n">
-        <v>1.90276047975593</v>
+        <v>-1.12054287352255</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0587722017556518</v>
+        <v>0.264360842367084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.237899593970079</v>
+        <v>0.36349615825474</v>
       </c>
     </row>
     <row r="10">
@@ -676,16 +670,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00997850330545454</v>
+        <v>-0.00669545094157566</v>
       </c>
       <c r="E10" t="n">
-        <v>1.72364603512933</v>
+        <v>-1.23851184972822</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0866005635299937</v>
+        <v>0.217555578192134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.237899593970079</v>
+        <v>0.341873051444781</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00207123429115956</v>
+        <v>0.00782933833598707</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.357776578761023</v>
+        <v>1.44825619502926</v>
       </c>
       <c r="F11" t="n">
-        <v>0.720956958362496</v>
+        <v>0.149734471077299</v>
       </c>
       <c r="G11" t="n">
-        <v>0.937244045871245</v>
+        <v>0.274513196975048</v>
       </c>
     </row>
     <row r="12">
@@ -722,62 +716,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0134891161737905</v>
+        <v>-0.00897101523441026</v>
       </c>
       <c r="E12" t="n">
-        <v>2.33005500911581</v>
+        <v>-1.65944142804739</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0209851044716819</v>
+        <v>0.0992184184649431</v>
       </c>
       <c r="G12" t="n">
-        <v>0.136403179065933</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.00758196482054729</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.3096777343635</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.192082473226099</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.356724593134183</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.00790147749053361</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.36486905213302</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.174108572005759</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.356724593134183</v>
+        <v>0.272850650778593</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +764,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -825,21 +773,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0000203867589102837</v>
+        <v>-0.0000254462711881958</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.576257617995246</v>
+        <v>-0.75776668487476</v>
       </c>
       <c r="F2" t="n">
-        <v>0.565207719324199</v>
+        <v>0.449837593916722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -848,21 +796,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0000468356911846199</v>
+        <v>0.000000087628929185142</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.32387026098571</v>
+        <v>0.00260950937277416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.187334026005784</v>
+        <v>0.997921551938635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.766616508174709</v>
+        <v>0.997921551938635</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -871,21 +819,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000497252664807705</v>
+        <v>-0.0000542041303981889</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.40554777453779</v>
+        <v>-1.61414943252701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.161694162925221</v>
+        <v>0.108699479784873</v>
       </c>
       <c r="G4" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -894,21 +842,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000122681770545669</v>
+        <v>0.0000247401769014283</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.346775596735119</v>
+        <v>0.736739842751776</v>
       </c>
       <c r="F5" t="n">
-        <v>0.72919132138088</v>
+        <v>0.462487548247203</v>
       </c>
       <c r="G5" t="n">
-        <v>0.795351457237365</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -917,21 +865,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0000191144736459425</v>
+        <v>-0.0000209339167057531</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.540294860056813</v>
+        <v>-0.623392895023517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.589705006288238</v>
+        <v>0.534019408682492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -940,21 +888,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000120335612901491</v>
+        <v>-0.0000191774863938112</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.340143884350502</v>
+        <v>-0.571088006623554</v>
       </c>
       <c r="F7" t="n">
-        <v>0.734170575911413</v>
+        <v>0.568836405744872</v>
       </c>
       <c r="G7" t="n">
-        <v>0.795351457237365</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -963,21 +911,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00000603161810923274</v>
+        <v>0.0000354614443005805</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.170491341933227</v>
+        <v>1.05600938109106</v>
       </c>
       <c r="F8" t="n">
-        <v>0.864827680402933</v>
+        <v>0.292744727518488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.864827680402933</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -986,21 +934,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000353448148704082</v>
+        <v>-0.0000124537410502971</v>
       </c>
       <c r="E9" t="n">
-        <v>0.999066056322974</v>
+        <v>-0.370861019289541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.319191017778334</v>
+        <v>0.711289867459032</v>
       </c>
       <c r="G9" t="n">
-        <v>0.766616508174709</v>
+        <v>0.782418854204935</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1009,21 +957,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000276351002658943</v>
+        <v>-0.0000191437266480784</v>
       </c>
       <c r="E10" t="n">
-        <v>0.781141186902987</v>
+        <v>-0.570082672269576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.435812325189043</v>
+        <v>0.569516206665756</v>
       </c>
       <c r="G10" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1032,21 +980,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000326514427172449</v>
+        <v>0.0000361662570702001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.92293447365273</v>
+        <v>1.07699806080535</v>
       </c>
       <c r="F11" t="n">
-        <v>0.357357139111699</v>
+        <v>0.28329467862467</v>
       </c>
       <c r="G11" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1055,62 +1003,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000644924789944691</v>
+        <v>-0.0000429029655623579</v>
       </c>
       <c r="E12" t="n">
-        <v>1.82296178061018</v>
+        <v>-1.27761107885092</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0700763004422667</v>
+        <v>0.203456836898673</v>
       </c>
       <c r="G12" t="n">
-        <v>0.766616508174709</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0000349108844670258</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.986800462673228</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.325151152656714</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.766616508174709</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000192293233258096</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.543541232039676</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.587473473142184</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.766616508174709</v>
+        <v>0.696075363702591</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1051,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1158,21 +1060,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00000984032018312921</v>
+        <v>-0.0000345311374224183</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.259209993609129</v>
+        <v>-0.957824582640187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.795788689659101</v>
+        <v>0.339767788320935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.795788689659101</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1181,21 +1083,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0000531518626328285</v>
+        <v>0.00000281493712708317</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.40010626859375</v>
+        <v>0.0780807172936147</v>
       </c>
       <c r="F3" t="n">
-        <v>0.163314640270116</v>
+        <v>0.937872994535857</v>
       </c>
       <c r="G3" t="n">
-        <v>0.691529575855151</v>
+        <v>0.937872994535857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1204,21 +1106,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0000509143266449762</v>
+        <v>-0.0000566213089357463</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.34116594162088</v>
+        <v>-1.57056169151014</v>
       </c>
       <c r="F4" t="n">
-        <v>0.181666235920245</v>
+        <v>0.118494556763587</v>
       </c>
       <c r="G4" t="n">
-        <v>0.691529575855151</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1227,21 +1129,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00000994829558018162</v>
+        <v>0.0000320393038005807</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.262054240692459</v>
+        <v>0.888706109372178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.793598761414806</v>
+        <v>0.375653519441073</v>
       </c>
       <c r="G5" t="n">
-        <v>0.795788689659101</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1250,21 +1152,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0000234068494597854</v>
+        <v>-0.0000252502922919822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.616574378269004</v>
+        <v>-0.70039252921941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.538345177776108</v>
+        <v>0.484820174093888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.777609701232155</v>
+        <v>0.65861173605684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1273,21 +1175,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0000129938370115369</v>
+        <v>-0.00000937389098165293</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.342278741548782</v>
+        <v>-0.26001295895302</v>
       </c>
       <c r="F7" t="n">
-        <v>0.732566429019316</v>
+        <v>0.795227773591728</v>
       </c>
       <c r="G7" t="n">
-        <v>0.795788689659101</v>
+        <v>0.874750550950901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1296,21 +1198,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0000161339258702605</v>
+        <v>0.0000327595329388965</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.424993774988174</v>
+        <v>0.908683822975227</v>
       </c>
       <c r="F8" t="n">
-        <v>0.671381829544482</v>
+        <v>0.365045942819598</v>
       </c>
       <c r="G8" t="n">
-        <v>0.795788689659101</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1319,21 +1221,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000312329498200107</v>
+        <v>-0.0000222083326050139</v>
       </c>
       <c r="E9" t="n">
-        <v>0.822726554885814</v>
+        <v>-0.616014660864369</v>
       </c>
       <c r="F9" t="n">
-        <v>0.411822858391345</v>
+        <v>0.538864147682869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.691529575855151</v>
+        <v>0.65861173605684</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1342,21 +1244,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000347524182314973</v>
+        <v>-0.0000305786579819858</v>
       </c>
       <c r="E10" t="n">
-        <v>0.915435061059529</v>
+        <v>-0.848190720189761</v>
       </c>
       <c r="F10" t="n">
-        <v>0.361267628082365</v>
+        <v>0.397749279789169</v>
       </c>
       <c r="G10" t="n">
-        <v>0.691529575855151</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1365,21 +1267,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000457080768259932</v>
+        <v>0.0000375604497576575</v>
       </c>
       <c r="E11" t="n">
-        <v>1.20402487738805</v>
+        <v>1.04185163879222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.230263613714195</v>
+        <v>0.299238662390015</v>
       </c>
       <c r="G11" t="n">
-        <v>0.691529575855151</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1388,62 +1290,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000681252933621078</v>
+        <v>-0.0000433782388783357</v>
       </c>
       <c r="E12" t="n">
-        <v>1.79453071936492</v>
+        <v>-1.20322545536348</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0745158386709967</v>
+        <v>0.230877307571608</v>
       </c>
       <c r="G12" t="n">
-        <v>0.691529575855151</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0000362582053904904</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.955099937059042</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.340891337750562</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.691529575855151</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0000303227215250599</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.798749665300295</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.425556662064708</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.691529575855151</v>
+        <v>0.625034582525837</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1491,21 +1347,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0156162396506812</v>
+        <v>-0.0222154717487911</v>
       </c>
       <c r="E2" t="n">
-        <v>0.574577535002998</v>
+        <v>-0.850281234101241</v>
       </c>
       <c r="F2" t="n">
-        <v>0.566341097951223</v>
+        <v>0.39659016066147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.920304284170737</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1514,21 +1370,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0454625436509029</v>
+        <v>-0.00594983291143009</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.67273023789454</v>
+        <v>-0.227725583675812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0962305984387108</v>
+        <v>0.820184860022927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.573430172595506</v>
+        <v>0.90220334602522</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1537,21 +1393,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00573104617462989</v>
+        <v>-0.0509358162342738</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.210865769075436</v>
+        <v>-1.94953180276215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.833246056726977</v>
+        <v>0.0531886965973163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.986823072291263</v>
+        <v>0.585075662570479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1560,21 +1416,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00457208160200265</v>
+        <v>0.0386018311914378</v>
       </c>
       <c r="E5" t="n">
-        <v>0.168223300581626</v>
+        <v>1.47745737903628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.866608762662035</v>
+        <v>0.141752101316639</v>
       </c>
       <c r="G5" t="n">
-        <v>0.986823072291263</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1583,21 +1439,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000859274012225921</v>
+        <v>-0.000470381815242753</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0316157765813597</v>
+        <v>-0.0180035263210269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9748157687694</v>
+        <v>0.985661135361741</v>
       </c>
       <c r="G6" t="n">
-        <v>0.986823072291263</v>
+        <v>0.985661135361741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1606,21 +1462,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0204814290020186</v>
+        <v>0.0157643506757436</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.753585322238922</v>
+        <v>0.603369205882627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.452146857531592</v>
+        <v>0.547218938206923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.839701306844386</v>
+        <v>0.752426040034519</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1629,21 +1485,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000449535804017712</v>
+        <v>0.0291911894088281</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0165400365226094</v>
+        <v>1.11727182011213</v>
       </c>
       <c r="F8" t="n">
-        <v>0.986823072291263</v>
+        <v>0.265751757181527</v>
       </c>
       <c r="G8" t="n">
-        <v>0.986823072291263</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1652,21 +1508,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0375597044646129</v>
+        <v>-0.0286976404974036</v>
       </c>
       <c r="E9" t="n">
-        <v>1.38195640496443</v>
+        <v>-1.09838158981494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.168809020057505</v>
+        <v>0.273883817167278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.573430172595506</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1675,21 +1531,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0368943526918835</v>
+        <v>-0.0214158969713336</v>
       </c>
       <c r="E10" t="n">
-        <v>1.35747572395311</v>
+        <v>-0.819678083458276</v>
       </c>
       <c r="F10" t="n">
-        <v>0.17644005310631</v>
+        <v>0.413763732444988</v>
       </c>
       <c r="G10" t="n">
-        <v>0.573430172595506</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1698,21 +1554,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0838385746970638</v>
+        <v>0.0246822974869347</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.08472222924054</v>
+        <v>0.944697218450329</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00238074741903707</v>
+        <v>0.346406922831363</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0309497164474819</v>
+        <v>0.650200150984981</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1721,62 +1577,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.011737023130703</v>
+        <v>-0.00856341917288182</v>
       </c>
       <c r="E12" t="n">
-        <v>0.431847228882551</v>
+        <v>-0.327758721704409</v>
       </c>
       <c r="F12" t="n">
-        <v>0.666402897046466</v>
+        <v>0.743573468539582</v>
       </c>
       <c r="G12" t="n">
-        <v>0.962581962400451</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0244587867982558</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.899926598340381</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.369439847946368</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.800453003883797</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0304795698496379</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.12145282756293</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.263686093894961</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.685583844126899</v>
+        <v>0.90220334602522</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1824,21 +1634,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000561769443587532</v>
+        <v>-0.000460772580432708</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.347939760665752</v>
+        <v>-0.299604499168577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.728318418965757</v>
+        <v>0.764913885267713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.728318418965757</v>
+        <v>0.841405273794485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1847,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00105272111758357</v>
+        <v>0.00149748918737366</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.65201754541984</v>
+        <v>0.973700513108042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.515275634830707</v>
+        <v>0.331849468615948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1870,21 +1680,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00149171846535949</v>
+        <v>-0.00120709932049167</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.92391669170057</v>
+        <v>-0.784882613941594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.356846970733518</v>
+        <v>0.433820765433742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1893,21 +1703,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00141516746929603</v>
+        <v>-0.00145305184585568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.876503761800094</v>
+        <v>-0.9448063731022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.382000415221151</v>
+        <v>0.346351376137693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1916,21 +1726,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00100774832980785</v>
+        <v>-0.00116222822449063</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.624163020411806</v>
+        <v>-0.755706437199668</v>
       </c>
       <c r="F6" t="n">
-        <v>0.533362171650629</v>
+        <v>0.451068234619966</v>
       </c>
       <c r="G6" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1939,21 +1749,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000817967029162568</v>
+        <v>-0.000554668137402536</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.506619317956825</v>
+        <v>-0.360657462202276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.61308227696079</v>
+        <v>0.718887729137862</v>
       </c>
       <c r="G7" t="n">
-        <v>0.664172466707522</v>
+        <v>0.841405273794485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1962,21 +1772,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00128463506492865</v>
+        <v>-0.00149140296241734</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.795656691790967</v>
+        <v>-0.969743115343285</v>
       </c>
       <c r="F8" t="n">
-        <v>0.427347735178782</v>
+        <v>0.333811904750352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1985,21 +1795,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00132387510142363</v>
+        <v>-0.0000613771857078529</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.81996055712652</v>
+        <v>-0.03990880049136</v>
       </c>
       <c r="F9" t="n">
-        <v>0.41339353674173</v>
+        <v>0.968221498928086</v>
       </c>
       <c r="G9" t="n">
-        <v>0.664172466707522</v>
+        <v>0.968221498928086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2008,21 +1818,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.00125811743694996</v>
+        <v>0.00126585998292946</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.77923262808005</v>
+        <v>0.823090093266766</v>
       </c>
       <c r="F10" t="n">
-        <v>0.436932495863851</v>
+        <v>0.41182726446519</v>
       </c>
       <c r="G10" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2031,21 +1841,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00289230625440324</v>
+        <v>0.000979983829814647</v>
       </c>
       <c r="E11" t="n">
-        <v>1.79139032465428</v>
+        <v>0.637207110390981</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0750201304514387</v>
+        <v>0.525008796380779</v>
       </c>
       <c r="G11" t="n">
-        <v>0.664172466707522</v>
+        <v>0.721887095023572</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2054,62 +1864,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0012598429492778</v>
+        <v>-0.00141701640060212</v>
       </c>
       <c r="E12" t="n">
-        <v>0.780301348269847</v>
+        <v>-0.921375331443056</v>
       </c>
       <c r="F12" t="n">
-        <v>0.436305037009242</v>
+        <v>0.358406322403779</v>
       </c>
       <c r="G12" t="n">
-        <v>0.664172466707522</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.000915926192158977</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.567291695418874</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.571268790840702</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.664172466707522</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.00149734254177628</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.927400042076357</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.355041437534359</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.664172466707522</v>
+        <v>0.708821511545661</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +1912,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2157,21 +1921,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00584028857138172</v>
+        <v>0.0034031802770355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.731406551191115</v>
+        <v>0.441222416898059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.46562809698614</v>
+        <v>0.65977384644081</v>
       </c>
       <c r="G2" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2180,21 +1944,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000286200544149097</v>
+        <v>-0.0110705408927115</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0358422277232763</v>
+        <v>-1.43529593245818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.97145398423204</v>
+        <v>0.153568078936466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.97145398423204</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2203,21 +1967,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0080116664379552</v>
+        <v>-0.0020234763810881</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00333831917009</v>
+        <v>-0.262343768687314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.317251415048453</v>
+        <v>0.793465400010542</v>
       </c>
       <c r="G4" t="n">
-        <v>0.69880036380801</v>
+        <v>0.872811940011596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2226,21 +1990,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0100072163972591</v>
+        <v>0.00457628131680316</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.25325033903433</v>
+        <v>0.593314999099667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.211989734719703</v>
+        <v>0.553985615333243</v>
       </c>
       <c r="G5" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2249,21 +2013,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00566479935210049</v>
+        <v>0.00471673162220443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.70942921855131</v>
+        <v>0.611524385073543</v>
       </c>
       <c r="F6" t="n">
-        <v>0.479117132662135</v>
+        <v>0.54190424499944</v>
       </c>
       <c r="G6" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2272,21 +2036,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00638444179618716</v>
+        <v>0.00583893014618183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.799553395068782</v>
+        <v>0.757017454697247</v>
       </c>
       <c r="F7" t="n">
-        <v>0.425185368154285</v>
+        <v>0.45038853859696</v>
       </c>
       <c r="G7" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2295,21 +2059,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00143257745538023</v>
+        <v>0.0044798866955693</v>
       </c>
       <c r="E8" t="n">
-        <v>0.179408349972321</v>
+        <v>0.580817433794716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.857849889044084</v>
+        <v>0.562353840029884</v>
       </c>
       <c r="G8" t="n">
-        <v>0.97145398423204</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2318,21 +2082,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00587069505650219</v>
+        <v>-0.00301468749789815</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73521449700475</v>
+        <v>-0.390854317354493</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4633127366737</v>
+        <v>0.696535038279921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2341,21 +2105,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00339556583531742</v>
+        <v>-0.00594499281653175</v>
       </c>
       <c r="E10" t="n">
-        <v>0.425242531528596</v>
+        <v>-0.770768482837085</v>
       </c>
       <c r="F10" t="n">
-        <v>0.671245893812623</v>
+        <v>0.442221581328973</v>
       </c>
       <c r="G10" t="n">
-        <v>0.87261966195641</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2364,21 +2128,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0150691307576314</v>
+        <v>-0.00116919401807807</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.88717746086982</v>
+        <v>-0.151586036731658</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0609940580052238</v>
+        <v>0.879744877469453</v>
       </c>
       <c r="G11" t="n">
-        <v>0.69880036380801</v>
+        <v>0.879744877469453</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2387,62 +2151,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00560471108349105</v>
+        <v>0.00816738023164989</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.701904084686173</v>
+        <v>1.05890107257941</v>
       </c>
       <c r="F12" t="n">
-        <v>0.483784867251699</v>
+        <v>0.291578688877987</v>
       </c>
       <c r="G12" t="n">
-        <v>0.69880036380801</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.000905579903746326</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.113409990984466</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.909851336811547</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.97145398423204</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0077888190603779</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.975430103696888</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.33085710283176</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.69880036380801</v>
+        <v>0.851320602342125</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2199,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -2490,21 +2208,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0171827305047719</v>
+        <v>-0.111306484229624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17475319935611</v>
+        <v>-1.20414991244696</v>
       </c>
       <c r="F2" t="n">
-        <v>0.861482744123552</v>
+        <v>0.230520983757216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.913644599857403</v>
+        <v>0.422621803554896</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -2513,21 +2231,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.184370516120682</v>
+        <v>-0.0330148418637138</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.8750999761114</v>
+        <v>-0.357165345889709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0625040809980878</v>
+        <v>0.721494567153874</v>
       </c>
       <c r="G3" t="n">
-        <v>0.37018424273237</v>
+        <v>0.80186090061328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -2536,21 +2254,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0770428126562587</v>
+        <v>-0.20769839552278</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.783547061704517</v>
+        <v>-2.24694910197843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.43440265331513</v>
+        <v>0.0261748751907022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.627470499232965</v>
+        <v>0.287923627097724</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -2559,21 +2277,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0475408017586422</v>
+        <v>0.173702451536742</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.483503317762567</v>
+        <v>1.87916987278376</v>
       </c>
       <c r="F5" t="n">
-        <v>0.629364256321192</v>
+        <v>0.0622563450660177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.81817353321755</v>
+        <v>0.342409897863097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -2582,21 +2300,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0304322836089415</v>
+        <v>-0.0320920933077857</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.309504878918871</v>
+        <v>-0.347182750531301</v>
       </c>
       <c r="F6" t="n">
-        <v>0.757318777827581</v>
+        <v>0.728964455102982</v>
       </c>
       <c r="G6" t="n">
-        <v>0.895013101068959</v>
+        <v>0.80186090061328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -2605,21 +2323,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0878139037797858</v>
+        <v>0.0190070858416669</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.893092086220254</v>
+        <v>0.205624864629616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.373077832756406</v>
+        <v>0.837376387898667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.60625147822916</v>
+        <v>0.837376387898667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -2628,21 +2346,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01067866679913</v>
+        <v>0.137290183638978</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.108605043155835</v>
+        <v>1.48525006205077</v>
       </c>
       <c r="F8" t="n">
-        <v>0.913644599857403</v>
+        <v>0.139678756432121</v>
       </c>
       <c r="G8" t="n">
-        <v>0.913644599857403</v>
+        <v>0.422621803554896</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -2651,21 +2369,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.148477271009742</v>
+        <v>-0.0929750117275147</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5100555836228</v>
+        <v>-1.00583405366104</v>
       </c>
       <c r="F9" t="n">
-        <v>0.132896659320799</v>
+        <v>0.316194358679726</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395909823280649</v>
+        <v>0.496876849353855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2674,21 +2392,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.174674754245525</v>
+        <v>-0.118940705236947</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7764913523302</v>
+        <v>-1.28673940955662</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0774510942325012</v>
+        <v>0.200264246928014</v>
       </c>
       <c r="G10" t="n">
-        <v>0.37018424273237</v>
+        <v>0.422621803554896</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2697,21 +2415,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.104203373089207</v>
+        <v>0.118545458382515</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.05977759623129</v>
+        <v>1.28246349995033</v>
       </c>
       <c r="F11" t="n">
-        <v>0.29075807644763</v>
+        <v>0.201755094631625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.539979284831313</v>
+        <v>0.422621803554896</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2720,62 +2438,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.170119249789299</v>
+        <v>-0.0724966534140663</v>
       </c>
       <c r="E12" t="n">
-        <v>1.73016059144296</v>
+        <v>-0.7842924827376</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0854271329382393</v>
+        <v>0.434165760223921</v>
       </c>
       <c r="G12" t="n">
-        <v>0.37018424273237</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.116153656615784</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.18131533896095</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.23913719429684</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.518130587643153</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.14139589325299</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.43803598123784</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.152273008954096</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.395909823280649</v>
+        <v>0.596977920307891</v>
       </c>
     </row>
   </sheetData>
@@ -2791,45 +2463,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -2838,24 +2510,24 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00758196482054729</v>
+        <v>0.00782933833598707</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2864,24 +2536,24 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00584028857138172</v>
+        <v>0.00457628131680316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2890,24 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0012598429492778</v>
+        <v>0.00120709932049167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2916,24 +2588,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000276351002658943</v>
+        <v>0.0000247401769014283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2942,59 +2614,59 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000312329498200107</v>
+        <v>0.0000320393038005807</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0204814290020186</v>
+        <v>0.0222154717487911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.104203373089207</v>
+        <v>0.111306484229624</v>
       </c>
     </row>
   </sheetData>
